--- a/admin_v2/SALES_REPORT.xlsx
+++ b/admin_v2/SALES_REPORT.xlsx
@@ -15,15 +15,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="15">
   <si>
     <t>SALES REPORT</t>
   </si>
   <si>
-    <t>Amto.Robert (Arthur Murray Thousand Oaks) (Edwin Cabrera, Nicholas Kavoklis, Caleb Castillo)</t>
-  </si>
-  <si>
-    <t>(07/01/2025 - 10/27/2025)</t>
+    <t xml:space="preserve"> (Arthur Murray Thousand Oaks, Arthur Murray Woodland Hills, Demo 1, Demo 1) (Caleb Castillo)</t>
+  </si>
+  <si>
+    <t>(03/01/2026 - 03/21/2026)</t>
   </si>
   <si>
     <t>Date</t>
@@ -35,6 +35,9 @@
     <t>Amount of Sale</t>
   </si>
   <si>
+    <t>Service Provider Amount</t>
+  </si>
+  <si>
     <t>Enrollment Name</t>
   </si>
   <si>
@@ -53,70 +56,10 @@
     <t>Service Provider3</t>
   </si>
   <si>
-    <t>09/24/2025</t>
-  </si>
-  <si>
-    <t>Aar Bagnall</t>
-  </si>
-  <si>
-    <t>$29325.00</t>
-  </si>
-  <si>
-    <t>second -  - 13</t>
-  </si>
-  <si>
-    <t>PRI1: 0, GRP2: 0</t>
-  </si>
-  <si>
-    <t>Daisy Ramirez</t>
-  </si>
-  <si>
-    <t>Caleb Castillo (100%)</t>
-  </si>
-  <si>
-    <t>$59.00</t>
-  </si>
-  <si>
-    <t>$0.00</t>
-  </si>
-  <si>
-    <t>NEW -  - 11</t>
-  </si>
-  <si>
-    <t>GEN: 0</t>
-  </si>
-  <si>
-    <t>Nicholas Kavoklis (100%)</t>
-  </si>
-  <si>
-    <t>Time Exchange (100%)</t>
-  </si>
-  <si>
-    <t>09/02/2025</t>
-  </si>
-  <si>
-    <t>$2500.00</t>
-  </si>
-  <si>
-    <t>08/15/2025</t>
-  </si>
-  <si>
-    <t>$275.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - 9</t>
-  </si>
-  <si>
-    <t>PRI1: 0</t>
-  </si>
-  <si>
-    <t>Edwin Cabrera</t>
-  </si>
-  <si>
-    <t>Edwin Cabrera (100%)</t>
-  </si>
-  <si>
-    <t>Total: $32,159.00</t>
+    <t>Total: $0.00</t>
+  </si>
+  <si>
+    <t>Service Provider Total: $0.00</t>
   </si>
 </sst>
 </file>
@@ -170,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -182,12 +125,6 @@
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -491,7 +428,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="true" style="0"/>
@@ -501,7 +438,7 @@
     <col min="5" max="5" width="18" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -510,7 +447,7 @@
       <c r="D1"/>
       <c r="E1"/>
     </row>
-    <row r="2" spans="1:9" customHeight="1" ht="20">
+    <row r="2" spans="1:10" customHeight="1" ht="20">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -522,7 +459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3"/>
       <c r="B3"/>
       <c r="C3"/>
@@ -530,7 +467,7 @@
       <c r="E3"/>
       <c r="H3"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -558,176 +495,24 @@
       <c r="I4" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="J4" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="1:10">
+      <c r="C5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="C11" s="6" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
   <mergeCells>
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G2:J2"/>
     <mergeCell ref="H3:I3"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
